--- a/artfynd/A 35141-2022 artfynd.xlsx
+++ b/artfynd/A 35141-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35141-2022 artfynd.xlsx
+++ b/artfynd/A 35141-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104425315</v>
+        <v>104435439</v>
       </c>
       <c r="B2" t="n">
-        <v>88845</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4188</v>
+        <v>424</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Vitvär, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723747.446171707</v>
+        <v>723673</v>
       </c>
       <c r="R2" t="n">
-        <v>6362486.646863202</v>
+        <v>6362483</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,19 +743,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,49 +760,48 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Brian Johnson, Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104425297</v>
+        <v>104425590</v>
       </c>
       <c r="B3" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723720.6093191694</v>
+        <v>723583</v>
       </c>
       <c r="R3" t="n">
-        <v>6362472.202401207</v>
+        <v>6362534</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +845,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104425397</v>
+        <v>104425195</v>
       </c>
       <c r="B4" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90639</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6003295</v>
+        <v>970</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bittermusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Leucopaxillus gentianeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Quél.) Kotl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723686.6218874078</v>
+        <v>723712</v>
       </c>
       <c r="R4" t="n">
-        <v>6362479.533620784</v>
+        <v>6362419</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +943,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104425195</v>
+        <v>104435523</v>
       </c>
       <c r="B5" t="n">
-        <v>87960</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,20 +1001,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Vitvär, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723712.1581376576</v>
+        <v>723723</v>
       </c>
       <c r="R5" t="n">
-        <v>6362418.755492446</v>
+        <v>6362457</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,19 +1040,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,27 +1057,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Brian Johnson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Brian Johnson, Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104435423</v>
+        <v>104435501</v>
       </c>
       <c r="B6" t="n">
-        <v>85318</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>86826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3767</v>
+        <v>2033</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Dvärgfjällskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Lepiota echinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Quél. &amp; G.E. Bernard, 1888</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723721.0132175218</v>
+        <v>723735</v>
       </c>
       <c r="R6" t="n">
-        <v>6362454.9235446</v>
+        <v>6362405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,19 +1141,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,37 +1174,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104435499</v>
+        <v>104435443</v>
       </c>
       <c r="B7" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3286</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1283,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723632.297232175</v>
+        <v>723587</v>
       </c>
       <c r="R7" t="n">
-        <v>6362492.240286193</v>
+        <v>6362519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,19 +1242,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,37 +1275,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104435501</v>
+        <v>104435499</v>
       </c>
       <c r="B8" t="n">
-        <v>84614</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2033</v>
+        <v>3286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgfjällskivling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lepiota echinella</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Quél. &amp; G.E. Bernard, 1888</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723735.6390432499</v>
+        <v>723633</v>
       </c>
       <c r="R8" t="n">
-        <v>6362405.442650117</v>
+        <v>6362492</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,19 +1343,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,15 +1376,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104435471</v>
+        <v>104425010</v>
       </c>
       <c r="B9" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,37 +1387,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220686</v>
+        <v>3674</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vitvär, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723668.9166976444</v>
+        <v>723752</v>
       </c>
       <c r="R9" t="n">
-        <v>6362476.402246946</v>
+        <v>6362390</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,19 +1445,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,53 +1462,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Brian Johnson, Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104435458</v>
+        <v>104435527</v>
       </c>
       <c r="B10" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1509,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723633.5046750832</v>
+        <v>723591</v>
       </c>
       <c r="R10" t="n">
-        <v>6362499.875429751</v>
+        <v>6362521</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,19 +1542,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,37 +1575,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104435459</v>
+        <v>104435448</v>
       </c>
       <c r="B11" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1747,10 +1610,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723678.7675005775</v>
+        <v>723563</v>
       </c>
       <c r="R11" t="n">
-        <v>6362454.774424174</v>
+        <v>6362529</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,19 +1643,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,12 +1679,7 @@
         <v>104435449</v>
       </c>
       <c r="B12" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,10 +1711,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723632.6898843107</v>
+        <v>723632</v>
       </c>
       <c r="R12" t="n">
-        <v>6362494.965014279</v>
+        <v>6362495</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,19 +1744,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,37 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104435527</v>
+        <v>104435423</v>
       </c>
       <c r="B13" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87391</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1979,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723591.1898359971</v>
+        <v>723721</v>
       </c>
       <c r="R13" t="n">
-        <v>6362520.808586824</v>
+        <v>6362455</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,19 +1845,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,15 +1878,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104435433</v>
+        <v>104425315</v>
       </c>
       <c r="B14" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91322</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2071,37 +1889,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>4188</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vitvär, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723588.9410277961</v>
+        <v>723748</v>
       </c>
       <c r="R14" t="n">
-        <v>6362522.307522003</v>
+        <v>6362487</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2128,19 +1947,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,69 +1964,61 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Brian Johnson, Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104435439</v>
+        <v>104425586</v>
       </c>
       <c r="B15" t="n">
-        <v>85125</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91322</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>424</v>
+        <v>4188</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vitvär, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723672.85404947</v>
+        <v>723583</v>
       </c>
       <c r="R15" t="n">
-        <v>6362483.646154219</v>
+        <v>6362534</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2244,19 +2045,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,31 +2062,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Brian Johnson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Brian Johnson, Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104435420</v>
+        <v>104435433</v>
       </c>
       <c r="B16" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2303,21 +2085,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2327,10 +2109,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723722.2522147752</v>
+        <v>723589</v>
       </c>
       <c r="R16" t="n">
-        <v>6362432.283729601</v>
+        <v>6362523</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,19 +2142,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,15 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104435470</v>
+        <v>104435420</v>
       </c>
       <c r="B17" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,21 +2186,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220686</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2443,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723654.2346433558</v>
+        <v>723722</v>
       </c>
       <c r="R17" t="n">
-        <v>6362497.224991531</v>
+        <v>6362432</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,19 +2243,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2519,37 +2276,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104435523</v>
+        <v>104435462</v>
       </c>
       <c r="B18" t="n">
-        <v>87960</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>970</v>
+        <v>219862</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bittermusseron</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucopaxillus gentianeus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Quél.) Kotl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2559,10 +2311,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723723.0556133802</v>
+        <v>723569</v>
       </c>
       <c r="R18" t="n">
-        <v>6362457.197942489</v>
+        <v>6362525</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2592,19 +2344,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2635,15 +2377,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104435443</v>
+        <v>104435470</v>
       </c>
       <c r="B19" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,21 +2388,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3215</v>
+        <v>220686</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2675,10 +2412,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723586.9870451401</v>
+        <v>723654</v>
       </c>
       <c r="R19" t="n">
-        <v>6362518.41613139</v>
+        <v>6362497</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2708,19 +2445,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,6 +2471,606 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>104435471</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vitvär, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>723669</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6362477</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>104425297</v>
+      </c>
+      <c r="B21" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>723721</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6362472</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Brian Johnson, Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>104425397</v>
+      </c>
+      <c r="B22" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>723687</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6362480</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Brian Johnson, Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>104435458</v>
+      </c>
+      <c r="B23" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vitvär, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>723633</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6362500</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>104435459</v>
+      </c>
+      <c r="B24" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vitvär, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>723679</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6362455</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>104435507</v>
+      </c>
+      <c r="B25" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vitvär, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>723578</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6362532</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ardre</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>

--- a/artfynd/A 35141-2022 artfynd.xlsx
+++ b/artfynd/A 35141-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435439</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104425590</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104425195</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435523</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435501</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435443</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435499</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1471,6 +1511,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104425010</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1572,6 +1617,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435527</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1673,6 +1723,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435448</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435449</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1875,6 +1935,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435423</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104425315</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2071,6 +2141,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104425586</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435433</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2273,6 +2353,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435420</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2374,6 +2459,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435462</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2475,6 +2565,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435470</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2576,6 +2671,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435471</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2674,6 +2774,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104425297</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2772,6 +2877,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104425397</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2873,6 +2983,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435458</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2974,6 +3089,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435459</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3075,8 +3195,39 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104435507</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>